--- a/artfynd/A 25919-2020 artfynd.xlsx
+++ b/artfynd/A 25919-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 25919-2020 artfynd.xlsx
+++ b/artfynd/A 25919-2020 artfynd.xlsx
@@ -2694,7 +2694,7 @@
         <v>91962593</v>
       </c>
       <c r="B20" t="n">
-        <v>56395</v>
+        <v>57478</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2736,10 +2736,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>632794.9428760954</v>
+        <v>632795</v>
       </c>
       <c r="R20" t="n">
-        <v>6940090.888773011</v>
+        <v>6940091</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2769,19 +2769,9 @@
           <t>2020-06-09</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2020-06-09</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 25919-2020 artfynd.xlsx
+++ b/artfynd/A 25919-2020 artfynd.xlsx
@@ -2698,7 +2698,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">

--- a/artfynd/A 25919-2020 artfynd.xlsx
+++ b/artfynd/A 25919-2020 artfynd.xlsx
@@ -2694,7 +2694,7 @@
         <v>91962593</v>
       </c>
       <c r="B20" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>

--- a/artfynd/A 25919-2020 artfynd.xlsx
+++ b/artfynd/A 25919-2020 artfynd.xlsx
@@ -2694,7 +2694,7 @@
         <v>91962593</v>
       </c>
       <c r="B20" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>

--- a/artfynd/A 25919-2020 artfynd.xlsx
+++ b/artfynd/A 25919-2020 artfynd.xlsx
@@ -2694,7 +2694,7 @@
         <v>91962593</v>
       </c>
       <c r="B20" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>

--- a/artfynd/A 25919-2020 artfynd.xlsx
+++ b/artfynd/A 25919-2020 artfynd.xlsx
@@ -2694,7 +2694,7 @@
         <v>91962593</v>
       </c>
       <c r="B20" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
